--- a/詳細設計/01B_API詳細設計書テンプレート.xlsx
+++ b/詳細設計/01B_API詳細設計書テンプレート.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R76a69cbcaf0e454e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rd1be2d84637a4d15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_API一覧" sheetId="3" r:id="R0437e82a44dd4504"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_APIインターフェース" sheetId="4" r:id="R43714a88f6514492"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_処理業務フロー" sheetId="5" r:id="Rc802ad7e7aff47e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SQL_Parameter" sheetId="6" r:id="R48fe45709040427a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_単体テスト観点" sheetId="7" r:id="R5bed203e97ee45a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re6d42936552846c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Redb4abea3c354e31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_API一覧" sheetId="3" r:id="R42b1e0e146164f95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_APIインターフェース" sheetId="4" r:id="R40ca6b81a80b42e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_処理業務フロー" sheetId="5" r:id="Red7bb58f6a3f499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SQL_Parameter" sheetId="6" r:id="R0eefa97f90004449"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_単体テスト観点" sheetId="7" r:id="R7744f68dc1654fd7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,6 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
@@ -344,7 +347,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="131">
+  <x:cellXfs count="132">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -732,6 +735,9 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="4" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1273,9 +1279,10 @@
       <x:c r="K21" s="2"/>
       <x:c r="L21" s="2"/>
     </x:row>
-    <x:row r="22">
+    <x:row r="22" ht="72" customHeight="1">
       <x:c r="A22" s="53" t="str">
-        <x:v>03は入出力契約、04はRequest受信からResponse返却までの連続した処理業務フロー、05はSQLとParameterの業務説明、06は単体テスト観点を記載する。Java Class・Method名は本書では固定しない。</x:v>
+        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
+03は入出力契約、04はRequest受信からResponse返却までの連続した処理業務フロー、05はSQLとParameterの業務説明、06は単体テスト観点を記載する。Java Class・Method名は本書では固定しない。</x:v>
       </x:c>
       <x:c r="B22" s="54"/>
       <x:c r="C22" s="54"/>
@@ -1569,30 +1576,30 @@
       <x:c r="K8" s="2"/>
       <x:c r="L8" s="2"/>
     </x:row>
-    <x:row r="9" ht="24" hidden="0" customHeight="1">
+    <x:row r="9" ht="84" hidden="0" customHeight="1">
       <x:c r="A9" s="73" t="str">
-        <x:v>&lt;&lt;Ver.x.x&gt;&gt;</x:v>
-      </x:c>
-      <x:c r="B9" s="73" t="str">
-        <x:v>&lt;&lt;yyyy-mm-dd&gt;&gt;</x:v>
+        <x:v>Ver.2.0</x:v>
+      </x:c>
+      <x:c r="B9" s="131" t="n">
+        <x:v>46295</x:v>
       </x:c>
       <x:c r="C9" s="73" t="str">
-        <x:v>&lt;&lt;新規／改訂／削除&gt;&gt;</x:v>
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="D9" s="73" t="str">
-        <x:v>&lt;&lt;改訂内容&gt;&gt;</x:v>
+        <x:v>二次Review完了。設計内容変更なし。Review済／承認待ちへ整理。</x:v>
       </x:c>
       <x:c r="E9" s="73" t="str">
-        <x:v>&lt;&lt;記入&gt;&gt;</x:v>
+        <x:v>－</x:v>
       </x:c>
       <x:c r="F9" s="73" t="str">
-        <x:v>&lt;&lt;記入&gt;&gt;</x:v>
+        <x:v>Review済</x:v>
       </x:c>
       <x:c r="G9" s="73" t="str">
-        <x:v>&lt;&lt;記入&gt;&gt;</x:v>
+        <x:v>－</x:v>
       </x:c>
       <x:c r="H9" s="73" t="str">
-        <x:v>&lt;&lt;状態&gt;&gt;</x:v>
+        <x:v>承認待ち</x:v>
       </x:c>
       <x:c r="I9" s="2"/>
       <x:c r="J9" s="2"/>

--- a/詳細設計/01B_API詳細設計書テンプレート.xlsx
+++ b/詳細設計/01B_API詳細設計書テンプレート.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re6d42936552846c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Redb4abea3c354e31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_API一覧" sheetId="3" r:id="R42b1e0e146164f95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_APIインターフェース" sheetId="4" r:id="R40ca6b81a80b42e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_処理業務フロー" sheetId="5" r:id="Red7bb58f6a3f499d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SQL_Parameter" sheetId="6" r:id="R0eefa97f90004449"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_単体テスト観点" sheetId="7" r:id="R7744f68dc1654fd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R76a69cbcaf0e454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rd1be2d84637a4d15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_API一覧" sheetId="3" r:id="R0437e82a44dd4504"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_APIインターフェース" sheetId="4" r:id="R43714a88f6514492"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_処理業務フロー" sheetId="5" r:id="Rc802ad7e7aff47e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SQL_Parameter" sheetId="6" r:id="R48fe45709040427a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_単体テスト観点" sheetId="7" r:id="R5bed203e97ee45a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,9 +19,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
-  </x:numFmts>
   <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
@@ -347,7 +344,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="132">
+  <x:cellXfs count="131">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -735,9 +732,6 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="4" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1279,10 +1273,9 @@
       <x:c r="K21" s="2"/>
       <x:c r="L21" s="2"/>
     </x:row>
-    <x:row r="22" ht="72" customHeight="1">
+    <x:row r="22">
       <x:c r="A22" s="53" t="str">
-        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
-03は入出力契約、04はRequest受信からResponse返却までの連続した処理業務フロー、05はSQLとParameterの業務説明、06は単体テスト観点を記載する。Java Class・Method名は本書では固定しない。</x:v>
+        <x:v>03は入出力契約、04はRequest受信からResponse返却までの連続した処理業務フロー、05はSQLとParameterの業務説明、06は単体テスト観点を記載する。Java Class・Method名は本書では固定しない。</x:v>
       </x:c>
       <x:c r="B22" s="54"/>
       <x:c r="C22" s="54"/>
@@ -1576,30 +1569,30 @@
       <x:c r="K8" s="2"/>
       <x:c r="L8" s="2"/>
     </x:row>
-    <x:row r="9" ht="84" hidden="0" customHeight="1">
+    <x:row r="9" ht="24" hidden="0" customHeight="1">
       <x:c r="A9" s="73" t="str">
-        <x:v>Ver.2.0</x:v>
-      </x:c>
-      <x:c r="B9" s="131" t="n">
-        <x:v>46295</x:v>
+        <x:v>&lt;&lt;Ver.x.x&gt;&gt;</x:v>
+      </x:c>
+      <x:c r="B9" s="73" t="str">
+        <x:v>&lt;&lt;yyyy-mm-dd&gt;&gt;</x:v>
       </x:c>
       <x:c r="C9" s="73" t="str">
-        <x:v>Review</x:v>
+        <x:v>&lt;&lt;新規／改訂／削除&gt;&gt;</x:v>
       </x:c>
       <x:c r="D9" s="73" t="str">
-        <x:v>二次Review完了。設計内容変更なし。Review済／承認待ちへ整理。</x:v>
+        <x:v>&lt;&lt;改訂内容&gt;&gt;</x:v>
       </x:c>
       <x:c r="E9" s="73" t="str">
-        <x:v>－</x:v>
+        <x:v>&lt;&lt;記入&gt;&gt;</x:v>
       </x:c>
       <x:c r="F9" s="73" t="str">
-        <x:v>Review済</x:v>
+        <x:v>&lt;&lt;記入&gt;&gt;</x:v>
       </x:c>
       <x:c r="G9" s="73" t="str">
-        <x:v>－</x:v>
+        <x:v>&lt;&lt;記入&gt;&gt;</x:v>
       </x:c>
       <x:c r="H9" s="73" t="str">
-        <x:v>承認待ち</x:v>
+        <x:v>&lt;&lt;状態&gt;&gt;</x:v>
       </x:c>
       <x:c r="I9" s="2"/>
       <x:c r="J9" s="2"/>

--- a/詳細設計/01B_API詳細設計書テンプレート.xlsx
+++ b/詳細設計/01B_API詳細設計書テンプレート.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re6d42936552846c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Redb4abea3c354e31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_API一覧" sheetId="3" r:id="R42b1e0e146164f95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_APIインターフェース" sheetId="4" r:id="R40ca6b81a80b42e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_処理業務フロー" sheetId="5" r:id="Red7bb58f6a3f499d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SQL_Parameter" sheetId="6" r:id="R0eefa97f90004449"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_単体テスト観点" sheetId="7" r:id="R7744f68dc1654fd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9f6ccaf507ae4759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R4b8bf57ea00c4966"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_API一覧" sheetId="3" r:id="Rd170557c4dd84844"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_APIインターフェース" sheetId="4" r:id="R4d901a1d544141e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_処理業務フロー" sheetId="5" r:id="Ra8ac9f342f6143a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SQL_Parameter" sheetId="6" r:id="R2d0e87d846a148d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_単体テスト観点" sheetId="7" r:id="R6acd1d0ddacd441d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1170,7 +1170,7 @@
       <x:c r="D15" s="36"/>
       <x:c r="E15" s="36"/>
       <x:c r="F15" s="38" t="str">
-        <x:v>Ver.2.0</x:v>
+        <x:v>Ver.2.1</x:v>
       </x:c>
       <x:c r="G15" s="38"/>
       <x:c r="H15" s="38"/>
@@ -1281,7 +1281,7 @@
     </x:row>
     <x:row r="22" ht="72" customHeight="1">
       <x:c r="A22" s="53" t="str">
-        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
+        <x:v>文書状態：修正済／Review待ち。改訂日：2026-10-15。
 03は入出力契約、04はRequest受信からResponse返却までの連続した処理業務フロー、05はSQLとParameterの業務説明、06は単体テスト観点を記載する。Java Class・Method名は本書では固定しない。</x:v>
       </x:c>
       <x:c r="B22" s="54"/>
@@ -1453,7 +1453,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.0</x:v>
+        <x:v>Ver.2.1</x:v>
       </x:c>
       <x:c r="K2" s="61"/>
       <x:c r="L2" s="61"/>
@@ -1607,14 +1607,30 @@
       <x:c r="L9" s="2"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="2"/>
-      <x:c r="B10" s="2"/>
-      <x:c r="C10" s="2"/>
-      <x:c r="D10" s="2"/>
-      <x:c r="E10" s="2"/>
-      <x:c r="F10" s="2"/>
-      <x:c r="G10" s="2"/>
-      <x:c r="H10" s="2"/>
+      <x:c r="A10" s="73" t="str">
+        <x:v>Ver.2.1</x:v>
+      </x:c>
+      <x:c r="B10" s="131" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="C10" s="73" t="str">
+        <x:v>改訂</x:v>
+      </x:c>
+      <x:c r="D10" s="73" t="str">
+        <x:v>単体テスト観点のTest IDと具体的入力・期待値、正本根拠を明確化。</x:v>
+      </x:c>
+      <x:c r="E10" s="73" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="F10" s="73" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G10" s="73" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H10" s="73" t="str">
+        <x:v>Review待ち</x:v>
+      </x:c>
       <x:c r="I10" s="2"/>
       <x:c r="J10" s="2"/>
       <x:c r="K10" s="2"/>
@@ -1892,7 +1908,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.0</x:v>
+        <x:v>Ver.2.1</x:v>
       </x:c>
       <x:c r="K2" s="61"/>
       <x:c r="L2" s="61"/>
@@ -2500,7 +2516,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.0</x:v>
+        <x:v>Ver.2.1</x:v>
       </x:c>
       <x:c r="K2" s="61"/>
       <x:c r="L2" s="61"/>
@@ -5449,7 +5465,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.0</x:v>
+        <x:v>Ver.2.1</x:v>
       </x:c>
       <x:c r="K2" s="61"/>
       <x:c r="L2" s="61"/>
@@ -6953,7 +6969,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.0</x:v>
+        <x:v>Ver.2.1</x:v>
       </x:c>
       <x:c r="K2" s="61"/>
       <x:c r="L2" s="61"/>
@@ -8918,7 +8934,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="J2" s="61" t="str">
-        <x:v>Ver.2.0</x:v>
+        <x:v>Ver.2.1</x:v>
       </x:c>
       <x:c r="K2" s="61"/>
       <x:c r="L2" s="61"/>
@@ -8953,7 +8969,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="53" t="str">
-        <x:v>本Sheetは観点定義であり、実施用ケースはプロジェクト単体テスト仕様書へ展開する。各処理Step、入力項目、権限、SQL、Transaction、排他、異常、ログを最低1件以上追跡する。</x:v>
+        <x:v>本Sheetは観点定義であり、実施結果は単体テスト仕様書で管理する。各Step・入力・権限・SQL・TX・排他・異常・Logを対象に、具体的なFixture／入力／期待値を記載する。根拠は基本設計File名／Sheet名／設計ID又はCell位置で示す。</x:v>
       </x:c>
       <x:c r="B5" s="54"/>
       <x:c r="C5" s="54"/>
@@ -9013,7 +9029,7 @@
     </x:row>
     <x:row r="9" ht="24" hidden="0" customHeight="1">
       <x:c r="A9" s="68" t="str">
-        <x:v>No.</x:v>
+        <x:v>Test ID</x:v>
       </x:c>
       <x:c r="B9" s="68" t="str">
         <x:v>対象Step／項目／SQL</x:v>
@@ -9050,8 +9066,8 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="24" hidden="0" customHeight="1">
-      <x:c r="A10" s="71" t="n">
-        <x:v>1</x:v>
+      <x:c r="A10" s="71" t="str">
+        <x:v>UT-001</x:v>
       </x:c>
       <x:c r="B10" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9088,8 +9104,8 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="24" hidden="0" customHeight="1">
-      <x:c r="A11" s="72" t="n">
-        <x:v>2</x:v>
+      <x:c r="A11" s="72" t="str">
+        <x:v>UT-002</x:v>
       </x:c>
       <x:c r="B11" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9126,8 +9142,8 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="24" hidden="0" customHeight="1">
-      <x:c r="A12" s="71" t="n">
-        <x:v>3</x:v>
+      <x:c r="A12" s="71" t="str">
+        <x:v>UT-003</x:v>
       </x:c>
       <x:c r="B12" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9164,8 +9180,8 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="24" hidden="0" customHeight="1">
-      <x:c r="A13" s="72" t="n">
-        <x:v>4</x:v>
+      <x:c r="A13" s="72" t="str">
+        <x:v>UT-004</x:v>
       </x:c>
       <x:c r="B13" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9202,8 +9218,8 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="24" hidden="0" customHeight="1">
-      <x:c r="A14" s="71" t="n">
-        <x:v>5</x:v>
+      <x:c r="A14" s="71" t="str">
+        <x:v>UT-005</x:v>
       </x:c>
       <x:c r="B14" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9240,8 +9256,8 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="24" hidden="0" customHeight="1">
-      <x:c r="A15" s="72" t="n">
-        <x:v>6</x:v>
+      <x:c r="A15" s="72" t="str">
+        <x:v>UT-006</x:v>
       </x:c>
       <x:c r="B15" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9278,8 +9294,8 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="24" hidden="0" customHeight="1">
-      <x:c r="A16" s="71" t="n">
-        <x:v>7</x:v>
+      <x:c r="A16" s="71" t="str">
+        <x:v>UT-007</x:v>
       </x:c>
       <x:c r="B16" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9316,8 +9332,8 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="24" hidden="0" customHeight="1">
-      <x:c r="A17" s="72" t="n">
-        <x:v>8</x:v>
+      <x:c r="A17" s="72" t="str">
+        <x:v>UT-008</x:v>
       </x:c>
       <x:c r="B17" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9354,8 +9370,8 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="24" hidden="0" customHeight="1">
-      <x:c r="A18" s="71" t="n">
-        <x:v>9</x:v>
+      <x:c r="A18" s="71" t="str">
+        <x:v>UT-009</x:v>
       </x:c>
       <x:c r="B18" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9392,8 +9408,8 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="24" hidden="0" customHeight="1">
-      <x:c r="A19" s="72" t="n">
-        <x:v>10</x:v>
+      <x:c r="A19" s="72" t="str">
+        <x:v>UT-010</x:v>
       </x:c>
       <x:c r="B19" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9430,8 +9446,8 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="24" hidden="0" customHeight="1">
-      <x:c r="A20" s="71" t="n">
-        <x:v>11</x:v>
+      <x:c r="A20" s="71" t="str">
+        <x:v>UT-011</x:v>
       </x:c>
       <x:c r="B20" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9468,8 +9484,8 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="24" hidden="0" customHeight="1">
-      <x:c r="A21" s="72" t="n">
-        <x:v>12</x:v>
+      <x:c r="A21" s="72" t="str">
+        <x:v>UT-012</x:v>
       </x:c>
       <x:c r="B21" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9506,8 +9522,8 @@
       </x:c>
     </x:row>
     <x:row r="22" ht="24" hidden="0" customHeight="1">
-      <x:c r="A22" s="71" t="n">
-        <x:v>13</x:v>
+      <x:c r="A22" s="71" t="str">
+        <x:v>UT-013</x:v>
       </x:c>
       <x:c r="B22" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9544,8 +9560,8 @@
       </x:c>
     </x:row>
     <x:row r="23" ht="24" hidden="0" customHeight="1">
-      <x:c r="A23" s="72" t="n">
-        <x:v>14</x:v>
+      <x:c r="A23" s="72" t="str">
+        <x:v>UT-014</x:v>
       </x:c>
       <x:c r="B23" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9582,8 +9598,8 @@
       </x:c>
     </x:row>
     <x:row r="24" ht="24" hidden="0" customHeight="1">
-      <x:c r="A24" s="71" t="n">
-        <x:v>15</x:v>
+      <x:c r="A24" s="71" t="str">
+        <x:v>UT-015</x:v>
       </x:c>
       <x:c r="B24" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9620,8 +9636,8 @@
       </x:c>
     </x:row>
     <x:row r="25" ht="24" hidden="0" customHeight="1">
-      <x:c r="A25" s="72" t="n">
-        <x:v>16</x:v>
+      <x:c r="A25" s="72" t="str">
+        <x:v>UT-016</x:v>
       </x:c>
       <x:c r="B25" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9658,8 +9674,8 @@
       </x:c>
     </x:row>
     <x:row r="26" ht="24" hidden="0" customHeight="1">
-      <x:c r="A26" s="71" t="n">
-        <x:v>17</x:v>
+      <x:c r="A26" s="71" t="str">
+        <x:v>UT-017</x:v>
       </x:c>
       <x:c r="B26" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9696,8 +9712,8 @@
       </x:c>
     </x:row>
     <x:row r="27" ht="24" hidden="0" customHeight="1">
-      <x:c r="A27" s="72" t="n">
-        <x:v>18</x:v>
+      <x:c r="A27" s="72" t="str">
+        <x:v>UT-018</x:v>
       </x:c>
       <x:c r="B27" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9734,8 +9750,8 @@
       </x:c>
     </x:row>
     <x:row r="28" ht="24" hidden="0" customHeight="1">
-      <x:c r="A28" s="71" t="n">
-        <x:v>19</x:v>
+      <x:c r="A28" s="71" t="str">
+        <x:v>UT-019</x:v>
       </x:c>
       <x:c r="B28" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9772,8 +9788,8 @@
       </x:c>
     </x:row>
     <x:row r="29" ht="24" hidden="0" customHeight="1">
-      <x:c r="A29" s="72" t="n">
-        <x:v>20</x:v>
+      <x:c r="A29" s="72" t="str">
+        <x:v>UT-020</x:v>
       </x:c>
       <x:c r="B29" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
@@ -9810,8 +9826,8 @@
       </x:c>
     </x:row>
     <x:row r="30" ht="24" hidden="0" customHeight="1">
-      <x:c r="A30" s="71" t="n">
-        <x:v>21</x:v>
+      <x:c r="A30" s="71" t="str">
+        <x:v>UT-021</x:v>
       </x:c>
       <x:c r="B30" s="73" t="str">
         <x:v>&lt;&lt;対象&gt;&gt;</x:v>
